--- a/source/8、绩效异常岗位/1、装车岗/装车岗-5月.xlsx
+++ b/source/8、绩效异常岗位/1、装车岗/装车岗-5月.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2366" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2562" uniqueCount="137">
   <si>
     <t>数据日期</t>
   </si>
@@ -434,6 +434,12 @@
   </si>
   <si>
     <t>113.9</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
   </si>
 </sst>
 </file>
@@ -1367,7 +1373,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H570"/>
+  <dimension ref="A1:H615"/>
   <sheetFormatPr defaultColWidth="12.6363636363636" defaultRowHeight="20" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="16384" width="12.6363636363636" style="1" customWidth="1"/>
@@ -16191,6 +16197,1176 @@
       </c>
       <c r="H570" s="1">
         <v>18.4</v>
+      </c>
+    </row>
+    <row r="571" customHeight="1" spans="1:8">
+      <c r="A571" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B571" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C571" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D571" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E571" s="1">
+        <v>165.8</v>
+      </c>
+      <c r="F571" s="1">
+        <v>24.6</v>
+      </c>
+      <c r="G571" s="1">
+        <v>153.6</v>
+      </c>
+      <c r="H571" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="572" customHeight="1" spans="1:8">
+      <c r="A572" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B572" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C572" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D572" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E572" s="1">
+        <v>160</v>
+      </c>
+      <c r="F572" s="1">
+        <v>22.4</v>
+      </c>
+      <c r="G572" s="1">
+        <v>153.6</v>
+      </c>
+      <c r="H572" s="1">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="573" customHeight="1" spans="1:8">
+      <c r="A573" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B573" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C573" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D573" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E573" s="1">
+        <v>135.5</v>
+      </c>
+      <c r="F573" s="1">
+        <v>13.6</v>
+      </c>
+      <c r="G573" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H573" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="574" customHeight="1" spans="1:8">
+      <c r="A574" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B574" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C574" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D574" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E574" s="1">
+        <v>174.8</v>
+      </c>
+      <c r="F574" s="1">
+        <v>13.4</v>
+      </c>
+      <c r="G574" s="1">
+        <v>153.6</v>
+      </c>
+      <c r="H574" s="1">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="575" customHeight="1" spans="1:8">
+      <c r="A575" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B575" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C575" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D575" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E575" s="1">
+        <v>116.3</v>
+      </c>
+      <c r="F575" s="1">
+        <v>11.8</v>
+      </c>
+      <c r="G575" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H575" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="576" customHeight="1" spans="1:8">
+      <c r="A576" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B576" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C576" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D576" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E576" s="1">
+        <v>188.8</v>
+      </c>
+      <c r="F576" s="1">
+        <v>11.2</v>
+      </c>
+      <c r="G576" s="1">
+        <v>153.6</v>
+      </c>
+      <c r="H576" s="1">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="577" customHeight="1" spans="1:8">
+      <c r="A577" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B577" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C577" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D577" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E577" s="1">
+        <v>119.5</v>
+      </c>
+      <c r="F577" s="1">
+        <v>11</v>
+      </c>
+      <c r="G577" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H577" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="578" customHeight="1" spans="1:8">
+      <c r="A578" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B578" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C578" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D578" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E578" s="1">
+        <v>236</v>
+      </c>
+      <c r="F578" s="1">
+        <v>10.9</v>
+      </c>
+      <c r="G578" s="1">
+        <v>153.6</v>
+      </c>
+      <c r="H578" s="1">
+        <v>53.6</v>
+      </c>
+    </row>
+    <row r="579" customHeight="1" spans="1:8">
+      <c r="A579" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B579" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C579" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D579" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E579" s="1">
+        <v>186.1</v>
+      </c>
+      <c r="F579" s="1">
+        <v>10.8</v>
+      </c>
+      <c r="G579" s="1">
+        <v>153.6</v>
+      </c>
+      <c r="H579" s="1">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="580" customHeight="1" spans="1:8">
+      <c r="A580" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B580" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C580" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D580" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E580" s="1">
+        <v>163.5</v>
+      </c>
+      <c r="F580" s="1">
+        <v>10.1</v>
+      </c>
+      <c r="G580" s="1">
+        <v>153.6</v>
+      </c>
+      <c r="H580" s="1">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="581" customHeight="1" spans="1:8">
+      <c r="A581" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B581" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C581" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D581" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E581" s="1">
+        <v>125.4</v>
+      </c>
+      <c r="F581" s="1">
+        <v>10</v>
+      </c>
+      <c r="G581" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H581" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="582" customHeight="1" spans="1:8">
+      <c r="A582" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B582" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C582" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D582" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E582" s="1">
+        <v>235.9</v>
+      </c>
+      <c r="F582" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="G582" s="1">
+        <v>153.6</v>
+      </c>
+      <c r="H582" s="1">
+        <v>53.6</v>
+      </c>
+    </row>
+    <row r="583" customHeight="1" spans="1:8">
+      <c r="A583" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B583" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C583" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D583" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E583" s="1">
+        <v>222.6</v>
+      </c>
+      <c r="F583" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="G583" s="1">
+        <v>153.6</v>
+      </c>
+      <c r="H583" s="1">
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="584" customHeight="1" spans="1:8">
+      <c r="A584" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B584" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C584" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D584" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E584" s="1">
+        <v>178.6</v>
+      </c>
+      <c r="F584" s="1">
+        <v>3.4</v>
+      </c>
+      <c r="G584" s="1">
+        <v>153.6</v>
+      </c>
+      <c r="H584" s="1">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="585" customHeight="1" spans="1:8">
+      <c r="A585" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B585" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C585" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D585" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E585" s="1">
+        <v>193.1</v>
+      </c>
+      <c r="F585" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="G585" s="1">
+        <v>153.6</v>
+      </c>
+      <c r="H585" s="1">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="586" customHeight="1" spans="1:8">
+      <c r="A586" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B586" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C586" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D586" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E586" s="1">
+        <v>170</v>
+      </c>
+      <c r="F586" s="1">
+        <v>2.4</v>
+      </c>
+      <c r="G586" s="1">
+        <v>153.6</v>
+      </c>
+      <c r="H586" s="1">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="587" customHeight="1" spans="1:8">
+      <c r="A587" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B587" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C587" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D587" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E587" s="1">
+        <v>201.2</v>
+      </c>
+      <c r="F587" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="G587" s="1">
+        <v>153.6</v>
+      </c>
+      <c r="H587" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="588" customHeight="1" spans="1:8">
+      <c r="A588" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B588" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C588" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D588" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E588" s="1">
+        <v>185.6</v>
+      </c>
+      <c r="F588" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G588" s="1">
+        <v>153.6</v>
+      </c>
+      <c r="H588" s="1">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="589" customHeight="1" spans="1:8">
+      <c r="A589" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B589" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C589" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D589" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E589" s="1">
+        <v>215.8</v>
+      </c>
+      <c r="F589" s="1">
+        <v>-0.1</v>
+      </c>
+      <c r="G589" s="1">
+        <v>153.6</v>
+      </c>
+      <c r="H589" s="1">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="590" customHeight="1" spans="1:8">
+      <c r="A590" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B590" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C590" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D590" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E590" s="1">
+        <v>223.8</v>
+      </c>
+      <c r="F590" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G590" s="1">
+        <v>153.6</v>
+      </c>
+      <c r="H590" s="1">
+        <v>45.7</v>
+      </c>
+    </row>
+    <row r="591" customHeight="1" spans="1:8">
+      <c r="A591" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B591" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C591" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D591" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E591" s="1">
+        <v>193.6</v>
+      </c>
+      <c r="F591" s="1">
+        <v>-3.1</v>
+      </c>
+      <c r="G591" s="1">
+        <v>153.6</v>
+      </c>
+      <c r="H591" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="592" customHeight="1" spans="1:8">
+      <c r="A592" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B592" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C592" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D592" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E592" s="1">
+        <v>176.2</v>
+      </c>
+      <c r="F592" s="1">
+        <v>-3.3</v>
+      </c>
+      <c r="G592" s="1">
+        <v>153.6</v>
+      </c>
+      <c r="H592" s="1">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="593" customHeight="1" spans="1:8">
+      <c r="A593" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B593" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C593" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D593" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E593" s="1">
+        <v>181.6</v>
+      </c>
+      <c r="F593" s="1">
+        <v>-9.2</v>
+      </c>
+      <c r="G593" s="1">
+        <v>153.6</v>
+      </c>
+      <c r="H593" s="1">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="594" customHeight="1" spans="1:8">
+      <c r="A594" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B594" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C594" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D594" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E594" s="1">
+        <v>165.4</v>
+      </c>
+      <c r="F594" s="1">
+        <v>24.3</v>
+      </c>
+      <c r="G594" s="1">
+        <v>153.4</v>
+      </c>
+      <c r="H594" s="1">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="595" customHeight="1" spans="1:8">
+      <c r="A595" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B595" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C595" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D595" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E595" s="1">
+        <v>159.6</v>
+      </c>
+      <c r="F595" s="1">
+        <v>22</v>
+      </c>
+      <c r="G595" s="1">
+        <v>153.4</v>
+      </c>
+      <c r="H595" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="596" customHeight="1" spans="1:8">
+      <c r="A596" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B596" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C596" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D596" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E596" s="1">
+        <v>174.7</v>
+      </c>
+      <c r="F596" s="1">
+        <v>13.3</v>
+      </c>
+      <c r="G596" s="1">
+        <v>153.4</v>
+      </c>
+      <c r="H596" s="1">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="597" customHeight="1" spans="1:8">
+      <c r="A597" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B597" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C597" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D597" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E597" s="1">
+        <v>134.6</v>
+      </c>
+      <c r="F597" s="1">
+        <v>12.8</v>
+      </c>
+      <c r="G597" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H597" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="598" customHeight="1" spans="1:8">
+      <c r="A598" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B598" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C598" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D598" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E598" s="1">
+        <v>116.1</v>
+      </c>
+      <c r="F598" s="1">
+        <v>11.7</v>
+      </c>
+      <c r="G598" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H598" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="599" customHeight="1" spans="1:8">
+      <c r="A599" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B599" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C599" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D599" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E599" s="1">
+        <v>119.9</v>
+      </c>
+      <c r="F599" s="1">
+        <v>11.3</v>
+      </c>
+      <c r="G599" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H599" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="600" customHeight="1" spans="1:8">
+      <c r="A600" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B600" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C600" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D600" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E600" s="1">
+        <v>188.8</v>
+      </c>
+      <c r="F600" s="1">
+        <v>11.2</v>
+      </c>
+      <c r="G600" s="1">
+        <v>153.4</v>
+      </c>
+      <c r="H600" s="1">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="601" customHeight="1" spans="1:8">
+      <c r="A601" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B601" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C601" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D601" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E601" s="1">
+        <v>186.1</v>
+      </c>
+      <c r="F601" s="1">
+        <v>10.8</v>
+      </c>
+      <c r="G601" s="1">
+        <v>153.4</v>
+      </c>
+      <c r="H601" s="1">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="602" customHeight="1" spans="1:8">
+      <c r="A602" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B602" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C602" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D602" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E602" s="1">
+        <v>235.5</v>
+      </c>
+      <c r="F602" s="1">
+        <v>10.7</v>
+      </c>
+      <c r="G602" s="1">
+        <v>153.4</v>
+      </c>
+      <c r="H602" s="1">
+        <v>53.4</v>
+      </c>
+    </row>
+    <row r="603" customHeight="1" spans="1:8">
+      <c r="A603" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B603" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C603" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D603" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E603" s="1">
+        <v>126</v>
+      </c>
+      <c r="F603" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="G603" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H603" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="604" customHeight="1" spans="1:8">
+      <c r="A604" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B604" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C604" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D604" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E604" s="1">
+        <v>235.1</v>
+      </c>
+      <c r="F604" s="1">
+        <v>6.4</v>
+      </c>
+      <c r="G604" s="1">
+        <v>153.4</v>
+      </c>
+      <c r="H604" s="1">
+        <v>53.2</v>
+      </c>
+    </row>
+    <row r="605" customHeight="1" spans="1:8">
+      <c r="A605" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B605" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C605" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D605" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E605" s="1">
+        <v>222.3</v>
+      </c>
+      <c r="F605" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="G605" s="1">
+        <v>153.4</v>
+      </c>
+      <c r="H605" s="1">
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="606" customHeight="1" spans="1:8">
+      <c r="A606" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B606" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C606" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D606" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E606" s="1">
+        <v>178.2</v>
+      </c>
+      <c r="F606" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="G606" s="1">
+        <v>153.4</v>
+      </c>
+      <c r="H606" s="1">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="607" customHeight="1" spans="1:8">
+      <c r="A607" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B607" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C607" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D607" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E607" s="1">
+        <v>193.1</v>
+      </c>
+      <c r="F607" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="G607" s="1">
+        <v>153.4</v>
+      </c>
+      <c r="H607" s="1">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="608" customHeight="1" spans="1:8">
+      <c r="A608" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B608" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C608" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D608" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E608" s="1">
+        <v>169.7</v>
+      </c>
+      <c r="F608" s="1">
+        <v>2.2</v>
+      </c>
+      <c r="G608" s="1">
+        <v>153.4</v>
+      </c>
+      <c r="H608" s="1">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="609" customHeight="1" spans="1:8">
+      <c r="A609" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B609" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C609" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D609" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E609" s="1">
+        <v>200</v>
+      </c>
+      <c r="F609" s="1">
+        <v>0</v>
+      </c>
+      <c r="G609" s="1">
+        <v>153.4</v>
+      </c>
+      <c r="H609" s="1">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="610" customHeight="1" spans="1:8">
+      <c r="A610" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B610" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C610" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D610" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E610" s="1">
+        <v>185.2</v>
+      </c>
+      <c r="F610" s="1">
+        <v>-0.1</v>
+      </c>
+      <c r="G610" s="1">
+        <v>153.4</v>
+      </c>
+      <c r="H610" s="1">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="611" customHeight="1" spans="1:8">
+      <c r="A611" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B611" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C611" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D611" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E611" s="1">
+        <v>215.7</v>
+      </c>
+      <c r="F611" s="1">
+        <v>-0.2</v>
+      </c>
+      <c r="G611" s="1">
+        <v>153.4</v>
+      </c>
+      <c r="H611" s="1">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="612" customHeight="1" spans="1:8">
+      <c r="A612" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B612" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C612" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D612" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E612" s="1">
+        <v>223.6</v>
+      </c>
+      <c r="F612" s="1">
+        <v>-1.1</v>
+      </c>
+      <c r="G612" s="1">
+        <v>153.4</v>
+      </c>
+      <c r="H612" s="1">
+        <v>45.7</v>
+      </c>
+    </row>
+    <row r="613" customHeight="1" spans="1:8">
+      <c r="A613" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B613" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C613" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D613" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E613" s="1">
+        <v>176.3</v>
+      </c>
+      <c r="F613" s="1">
+        <v>-3.3</v>
+      </c>
+      <c r="G613" s="1">
+        <v>153.4</v>
+      </c>
+      <c r="H613" s="1">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="614" customHeight="1" spans="1:8">
+      <c r="A614" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B614" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C614" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D614" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E614" s="1">
+        <v>193.3</v>
+      </c>
+      <c r="F614" s="1">
+        <v>-3.3</v>
+      </c>
+      <c r="G614" s="1">
+        <v>153.4</v>
+      </c>
+      <c r="H614" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="615" customHeight="1" spans="1:8">
+      <c r="A615" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B615" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C615" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D615" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E615" s="1">
+        <v>181.3</v>
+      </c>
+      <c r="F615" s="1">
+        <v>-9.4</v>
+      </c>
+      <c r="G615" s="1">
+        <v>153.4</v>
+      </c>
+      <c r="H615" s="1">
+        <v>18.1</v>
       </c>
     </row>
   </sheetData>
